--- a/UserScore/gs1.xlsx
+++ b/UserScore/gs1.xlsx
@@ -3000,7 +3000,9 @@
 and Developmental Issues, Urbanization, Their Problems and Their Remedies </t>
         </is>
       </c>
-      <c r="F113" t="inlineStr"/>
+      <c r="F113" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -14085,7 +14087,9 @@
           <t xml:space="preserve"> Investment Models </t>
         </is>
       </c>
-      <c r="F607" t="inlineStr"/>
+      <c r="F607" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="608">
       <c r="A608" t="n">

--- a/UserScore/gs1.xlsx
+++ b/UserScore/gs1.xlsx
@@ -481,7 +481,9 @@
 Modern Times</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -941,7 +943,9 @@
 Modern Times</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1240,7 +1244,9 @@
 different parts of the country</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
+      <c r="F35" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1748,7 +1754,9 @@
 different parts of the country</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr"/>
+      <c r="F57" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1771,7 +1779,9 @@
 different parts of the country</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr"/>
+      <c r="F58" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -2459,7 +2469,9 @@
           <t xml:space="preserve"> Salient Features of Indian Society; Diversity of India </t>
         </is>
       </c>
-      <c r="F89" t="inlineStr"/>
+      <c r="F89" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -3610,7 +3622,9 @@
           <t xml:space="preserve">Social Empowerment, Communalism, Regionalism &amp; Secularism </t>
         </is>
       </c>
-      <c r="F140" t="inlineStr"/>
+      <c r="F140" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -3742,7 +3756,9 @@
           <t xml:space="preserve">Social Empowerment, Communalism, Regionalism &amp; Secularism </t>
         </is>
       </c>
-      <c r="F146" t="inlineStr"/>
+      <c r="F146" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -4842,7 +4858,9 @@
           <t>Distribution of Key Natural Resources Across the World</t>
         </is>
       </c>
-      <c r="F196" t="inlineStr"/>
+      <c r="F196" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -5062,7 +5080,9 @@
           <t>Distribution of Key Natural Resources Across the World</t>
         </is>
       </c>
-      <c r="F206" t="inlineStr"/>
+      <c r="F206" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -5590,7 +5610,9 @@
           <t>Distribution of Key Natural Resources Across the World</t>
         </is>
       </c>
-      <c r="F230" t="inlineStr"/>
+      <c r="F230" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -5843,7 +5865,9 @@
 Cyclone etc</t>
         </is>
       </c>
-      <c r="F241" t="inlineStr"/>
+      <c r="F241" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -6690,7 +6714,9 @@
           <t>Functions and Responsibilities of the Union and the States</t>
         </is>
       </c>
-      <c r="F278" t="inlineStr"/>
+      <c r="F278" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -7066,7 +7092,9 @@
 Institutions </t>
         </is>
       </c>
-      <c r="F295" t="inlineStr"/>
+      <c r="F295" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -7443,7 +7471,9 @@
           <t xml:space="preserve">Parliament and State Legislatures </t>
         </is>
       </c>
-      <c r="F312" t="inlineStr"/>
+      <c r="F312" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -7531,7 +7561,9 @@
           <t xml:space="preserve">Parliament and State Legislatures </t>
         </is>
       </c>
-      <c r="F316" t="inlineStr"/>
+      <c r="F316" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -7918,7 +7950,9 @@
 Departments of the Government</t>
         </is>
       </c>
-      <c r="F333" t="inlineStr"/>
+      <c r="F333" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -8984,7 +9018,9 @@
 Arising Out of Their Design and Implementation </t>
         </is>
       </c>
-      <c r="F380" t="inlineStr"/>
+      <c r="F380" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -9409,7 +9445,9 @@
 the Performance of These Schemes</t>
         </is>
       </c>
-      <c r="F399" t="inlineStr"/>
+      <c r="F399" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -9777,7 +9815,9 @@
 Health, Education, Human Resources </t>
         </is>
       </c>
-      <c r="F415" t="inlineStr"/>
+      <c r="F415" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -9823,7 +9863,9 @@
 Health, Education, Human Resources </t>
         </is>
       </c>
-      <c r="F417" t="inlineStr"/>
+      <c r="F417" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
@@ -9913,7 +9955,9 @@
           <t xml:space="preserve">Issues Relating to Poverty and Hunger </t>
         </is>
       </c>
-      <c r="F421" t="inlineStr"/>
+      <c r="F421" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
@@ -10221,7 +10265,9 @@
           <t xml:space="preserve">Important Aspects of Governance, Transparency, and Accountability </t>
         </is>
       </c>
-      <c r="F435" t="inlineStr"/>
+      <c r="F435" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
@@ -10309,7 +10355,9 @@
           <t xml:space="preserve">Important Aspects of Governance, Transparency, and Accountability </t>
         </is>
       </c>
-      <c r="F439" t="inlineStr"/>
+      <c r="F439" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
@@ -10663,7 +10711,9 @@
 India’s Interests </t>
         </is>
       </c>
-      <c r="F455" t="inlineStr"/>
+      <c r="F455" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
@@ -10732,7 +10782,9 @@
 India’s Interests </t>
         </is>
       </c>
-      <c r="F458" t="inlineStr"/>
+      <c r="F458" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="n">
@@ -11307,7 +11359,9 @@
 Indian Diaspora </t>
         </is>
       </c>
-      <c r="F483" t="inlineStr"/>
+      <c r="F483" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="n">
@@ -11463,7 +11517,9 @@
           <t>Important International Institutions, Agencies, and Fora – Their Structure, Mandate</t>
         </is>
       </c>
-      <c r="F490" t="inlineStr"/>
+      <c r="F490" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="n">
@@ -11573,7 +11629,9 @@
           <t>Important International Institutions, Agencies, and Fora – Their Structure, Mandate</t>
         </is>
       </c>
-      <c r="F495" t="inlineStr"/>
+      <c r="F495" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="n">
@@ -11595,7 +11653,9 @@
           <t>Important International Institutions, Agencies, and Fora – Their Structure, Mandate</t>
         </is>
       </c>
-      <c r="F496" t="inlineStr"/>
+      <c r="F496" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="n">
@@ -11755,7 +11815,9 @@
 Development, and Employment </t>
         </is>
       </c>
-      <c r="F503" t="inlineStr"/>
+      <c r="F503" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="n">
@@ -11985,7 +12047,9 @@
 Development, and Employment </t>
         </is>
       </c>
-      <c r="F513" t="inlineStr"/>
+      <c r="F513" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="n">
@@ -12214,7 +12278,9 @@
           <t xml:space="preserve">Inclusive Growth and Issues Arising from It </t>
         </is>
       </c>
-      <c r="F523" t="inlineStr"/>
+      <c r="F523" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="n">
@@ -12830,7 +12896,9 @@
           <t xml:space="preserve"> Major Crops, Cropping Patterns, and Related Issues</t>
         </is>
       </c>
-      <c r="F551" t="inlineStr"/>
+      <c r="F551" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="552">
       <c r="A552" t="n">
@@ -12918,7 +12986,9 @@
           <t xml:space="preserve"> Major Crops, Cropping Patterns, and Related Issues</t>
         </is>
       </c>
-      <c r="F555" t="inlineStr"/>
+      <c r="F555" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="556">
       <c r="A556" t="n">
@@ -12962,7 +13032,9 @@
           <t xml:space="preserve"> Major Crops, Cropping Patterns, and Related Issues</t>
         </is>
       </c>
-      <c r="F557" t="inlineStr"/>
+      <c r="F557" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="558">
       <c r="A558" t="n">
@@ -13712,7 +13784,9 @@
 Industrial Growth </t>
         </is>
       </c>
-      <c r="F591" t="inlineStr"/>
+      <c r="F591" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="592">
       <c r="A592" t="n">
@@ -13847,7 +13921,9 @@
           <t xml:space="preserve"> Infrastructure: Energy, Ports, Roads, Airports, Railways, etc.</t>
         </is>
       </c>
-      <c r="F597" t="inlineStr"/>
+      <c r="F597" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="598">
       <c r="A598" t="n">
@@ -14203,7 +14279,9 @@
 Life</t>
         </is>
       </c>
-      <c r="F613" t="inlineStr"/>
+      <c r="F613" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="614">
       <c r="A614" t="n">
@@ -14433,7 +14511,9 @@
 Life</t>
         </is>
       </c>
-      <c r="F623" t="inlineStr"/>
+      <c r="F623" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="624">
       <c r="A624" t="n">
@@ -14594,7 +14674,9 @@
 Life</t>
         </is>
       </c>
-      <c r="F630" t="inlineStr"/>
+      <c r="F630" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="631">
       <c r="A631" t="n">
@@ -14709,7 +14791,9 @@
 Developing New Technology </t>
         </is>
       </c>
-      <c r="F635" t="inlineStr"/>
+      <c r="F635" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="636">
       <c r="A636" t="n">
@@ -15399,7 +15483,9 @@
 Assessment</t>
         </is>
       </c>
-      <c r="F665" t="inlineStr"/>
+      <c r="F665" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="666">
       <c r="A666" t="n">
@@ -17086,7 +17172,9 @@
           <t>Security Challenges and Their Management in Border Areas</t>
         </is>
       </c>
-      <c r="F741" t="inlineStr"/>
+      <c r="F741" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="742">
       <c r="A742" t="n">
@@ -17328,7 +17416,9 @@
           <t>Moral Thinkers and Philosophers</t>
         </is>
       </c>
-      <c r="F752" t="inlineStr"/>
+      <c r="F752" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="753">
       <c r="A753" t="n">
@@ -17394,7 +17484,9 @@
           <t>Emotional Intelligence</t>
         </is>
       </c>
-      <c r="F755" t="inlineStr"/>
+      <c r="F755" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="756">
       <c r="A756" t="n">
@@ -18166,7 +18258,9 @@
           <t>Case Studies</t>
         </is>
       </c>
-      <c r="F790" t="inlineStr"/>
+      <c r="F790" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="791">
       <c r="A791" t="n">
@@ -18430,7 +18524,9 @@
           <t>Human Values, Probity in Governance</t>
         </is>
       </c>
-      <c r="F802" t="inlineStr"/>
+      <c r="F802" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="803">
       <c r="A803" t="n">
@@ -18474,7 +18570,9 @@
           <t>Probity in Governance</t>
         </is>
       </c>
-      <c r="F804" t="inlineStr"/>
+      <c r="F804" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="805">
       <c r="A805" t="n">
@@ -18848,7 +18946,9 @@
           <t>Case Studies</t>
         </is>
       </c>
-      <c r="F821" t="inlineStr"/>
+      <c r="F821" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="822">
       <c r="A822" t="n">
@@ -20322,7 +20422,9 @@
           <t>Moral Thinkers and Philosophers</t>
         </is>
       </c>
-      <c r="F888" t="inlineStr"/>
+      <c r="F888" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="889">
       <c r="A889" t="n">
@@ -20608,7 +20710,9 @@
           <t>Human Values</t>
         </is>
       </c>
-      <c r="F901" t="inlineStr"/>
+      <c r="F901" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="902">
       <c r="A902" t="n">
@@ -21158,7 +21262,9 @@
           <t>Moral Thinkers and Philosophers</t>
         </is>
       </c>
-      <c r="F926" t="inlineStr"/>
+      <c r="F926" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="927">
       <c r="A927" t="n">
@@ -21444,7 +21550,9 @@
           <t>Aptitude and Foundational Values for Civil Service</t>
         </is>
       </c>
-      <c r="F939" t="inlineStr"/>
+      <c r="F939" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="940">
       <c r="A940" t="n">
@@ -21554,7 +21662,9 @@
           <t>Moral Thinkers and Philosophers</t>
         </is>
       </c>
-      <c r="F944" t="inlineStr"/>
+      <c r="F944" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="945">
       <c r="A945" t="n">
@@ -21840,7 +21950,9 @@
           <t>Ethics in Public Administration</t>
         </is>
       </c>
-      <c r="F957" t="inlineStr"/>
+      <c r="F957" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="958">
       <c r="A958" t="n">
@@ -22720,7 +22832,9 @@
           <t>Case Study</t>
         </is>
       </c>
-      <c r="F997" t="inlineStr"/>
+      <c r="F997" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="998">
       <c r="A998" t="n">
@@ -23116,7 +23230,9 @@
           <t>Case Study</t>
         </is>
       </c>
-      <c r="F1015" t="inlineStr"/>
+      <c r="F1015" t="n">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/UserScore/gs1.xlsx
+++ b/UserScore/gs1.xlsx
@@ -4948,7 +4948,9 @@
           <t>Distribution of Key Natural Resources Across the World</t>
         </is>
       </c>
-      <c r="F200" t="inlineStr"/>
+      <c r="F200" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -9911,7 +9913,9 @@
 Health, Education, Human Resources </t>
         </is>
       </c>
-      <c r="F419" t="inlineStr"/>
+      <c r="F419" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
@@ -10311,7 +10315,9 @@
           <t xml:space="preserve">Important Aspects of Governance, Transparency, and Accountability </t>
         </is>
       </c>
-      <c r="F437" t="inlineStr"/>
+      <c r="F437" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
@@ -11769,7 +11775,9 @@
 Development, and Employment </t>
         </is>
       </c>
-      <c r="F501" t="inlineStr"/>
+      <c r="F501" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="n">
@@ -16468,7 +16476,9 @@
           <t xml:space="preserve">Role of External State and Non-State Actors in Creating Challenges to Internal Security </t>
         </is>
       </c>
-      <c r="F709" t="inlineStr"/>
+      <c r="F709" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="710">
       <c r="A710" t="n">
@@ -16534,7 +16544,9 @@
           <t xml:space="preserve">Role of External State and Non-State Actors in Creating Challenges to Internal Security </t>
         </is>
       </c>
-      <c r="F712" t="inlineStr"/>
+      <c r="F712" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="713">
       <c r="A713" t="n">
@@ -17128,7 +17140,9 @@
           <t>Security Challenges and Their Management in Border Areas</t>
         </is>
       </c>
-      <c r="F739" t="inlineStr"/>
+      <c r="F739" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="740">
       <c r="A740" t="n">
@@ -17972,7 +17986,9 @@
           <t>Case Studies</t>
         </is>
       </c>
-      <c r="F777" t="inlineStr"/>
+      <c r="F777" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="778">
       <c r="A778" t="n">

--- a/UserScore/gs1.xlsx
+++ b/UserScore/gs1.xlsx
@@ -5458,7 +5458,9 @@
           <t>Distribution of Key Natural Resources Across the World</t>
         </is>
       </c>
-      <c r="F223" t="inlineStr"/>
+      <c r="F223" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -18940,7 +18942,9 @@
           <t>Case Studies</t>
         </is>
       </c>
-      <c r="F820" t="inlineStr"/>
+      <c r="F820" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="821">
       <c r="A821" t="n">
